--- a/resources/templates/CLUK_Import_Templates.xlsx
+++ b/resources/templates/CLUK_Import_Templates.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales items" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contacts" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Equipment'!$A$1:$Q$1</definedName>
@@ -29,7 +30,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -100,8 +101,15 @@
       <color rgb="FF555555"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -130,6 +138,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF8A8F8B"/>
         <bgColor rgb="FF808080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00327B1D"/>
       </patternFill>
     </fill>
   </fills>
@@ -161,7 +174,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -331,6 +344,8 @@
     <xf numFmtId="166" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -680,7 +695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="120" customWidth="1" style="29" min="1" max="1"/>
@@ -873,6 +888,14 @@
       <c r="A30" s="32" t="inlineStr">
         <is>
           <t>• Newsletter consent: Yes or No. Empty means No (GDPR).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="29" t="inlineStr">
+        <is>
+          <t>Equipment: Category and Sub-Category must come from the sheet "Lists" (or Settings › Product categories). New columns: Catalogue length (m), Frequency band, Frequency range, Connector, Colour, Truss series, Tags, Search words.</t>
         </is>
       </c>
     </row>
@@ -889,7 +912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Q501"/>
+  <dimension ref="A1:Y501"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" style="29" min="1" max="1"/>
@@ -907,6 +930,14 @@
     <col width="12" customWidth="1" style="29" min="15" max="15"/>
     <col width="16" customWidth="1" style="29" min="16" max="16"/>
     <col width="10" customWidth="1" style="29" min="17" max="17"/>
+    <col width="18" customWidth="1" style="30" min="18" max="18"/>
+    <col width="18" customWidth="1" style="30" min="19" max="19"/>
+    <col width="18" customWidth="1" style="30" min="20" max="20"/>
+    <col width="18" customWidth="1" style="30" min="21" max="21"/>
+    <col width="18" customWidth="1" style="30" min="22" max="22"/>
+    <col width="18" customWidth="1" style="30" min="23" max="23"/>
+    <col width="18" customWidth="1" style="30" min="24" max="24"/>
+    <col width="18" customWidth="1" style="30" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="30">
@@ -995,6 +1026,46 @@
           <t>Quantity</t>
         </is>
       </c>
+      <c r="R1" s="34" t="inlineStr">
+        <is>
+          <t>Catalogue length (m)</t>
+        </is>
+      </c>
+      <c r="S1" s="34" t="inlineStr">
+        <is>
+          <t>Frequency band</t>
+        </is>
+      </c>
+      <c r="T1" s="34" t="inlineStr">
+        <is>
+          <t>Frequency range</t>
+        </is>
+      </c>
+      <c r="U1" s="34" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="V1" s="34" t="inlineStr">
+        <is>
+          <t>Colour</t>
+        </is>
+      </c>
+      <c r="W1" s="34" t="inlineStr">
+        <is>
+          <t>Truss series</t>
+        </is>
+      </c>
+      <c r="X1" s="34" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="Y1" s="34" t="inlineStr">
+        <is>
+          <t>Search words</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="30">
       <c r="A2" s="36" t="inlineStr">
@@ -1004,12 +1075,12 @@
       </c>
       <c r="B2" s="36" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="C2" s="36" t="inlineStr">
         <is>
-          <t>Moving head · wash</t>
+          <t>Moving heads</t>
         </is>
       </c>
       <c r="D2" s="36" t="inlineStr">
@@ -1076,12 +1147,12 @@
       </c>
       <c r="B3" s="36" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="C3" s="36" t="inlineStr">
         <is>
-          <t>Moving head · wash</t>
+          <t>Moving heads</t>
         </is>
       </c>
       <c r="D3" s="36" t="inlineStr">
@@ -1148,12 +1219,12 @@
       </c>
       <c r="B4" s="36" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Rigging &amp; truss</t>
         </is>
       </c>
       <c r="C4" s="36" t="inlineStr">
         <is>
-          <t>Safety cable</t>
+          <t>Rigging hardware &amp; load cells</t>
         </is>
       </c>
       <c r="D4" s="36" t="inlineStr">
@@ -1205,13 +1276,41 @@
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="30">
-      <c r="A5" s="32" t="n"/>
-      <c r="B5" s="32" t="n"/>
-      <c r="C5" s="32" t="n"/>
-      <c r="D5" s="32" t="n"/>
-      <c r="E5" s="32" t="n"/>
-      <c r="F5" s="32" t="n"/>
-      <c r="G5" s="32" t="n"/>
+      <c r="A5" s="32" t="inlineStr">
+        <is>
+          <t>RIGSQUNEXNH34200</t>
+        </is>
+      </c>
+      <c r="B5" s="32" t="inlineStr">
+        <is>
+          <t>Rigging &amp; truss</t>
+        </is>
+      </c>
+      <c r="C5" s="32" t="inlineStr">
+        <is>
+          <t>Square truss</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="E5" s="32" t="inlineStr">
+        <is>
+          <t>NEXT</t>
+        </is>
+      </c>
+      <c r="F5" s="32" t="inlineStr">
+        <is>
+          <t>NH34 2 m</t>
+        </is>
+      </c>
+      <c r="G5" s="32" t="inlineStr">
+        <is>
+          <t>NEXT NH34 square truss 2 m, black</t>
+        </is>
+      </c>
       <c r="H5" s="42" t="n"/>
       <c r="I5" s="32" t="n"/>
       <c r="J5" s="43" t="n"/>
@@ -1224,16 +1323,66 @@
         <v/>
       </c>
       <c r="P5" s="43" t="n"/>
-      <c r="Q5" s="32" t="n"/>
+      <c r="Q5" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="R5" s="29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V5" s="29" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="W5" s="29" t="inlineStr">
+        <is>
+          <t>NH34</t>
+        </is>
+      </c>
+      <c r="Y5" s="29" t="inlineStr">
+        <is>
+          <t>truss, vierkant</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="30">
-      <c r="A6" s="32" t="n"/>
-      <c r="B6" s="32" t="n"/>
-      <c r="C6" s="32" t="n"/>
-      <c r="D6" s="32" t="n"/>
-      <c r="E6" s="32" t="n"/>
-      <c r="F6" s="32" t="n"/>
-      <c r="G6" s="32" t="n"/>
+      <c r="A6" s="32" t="inlineStr">
+        <is>
+          <t>CABDATNEU8WAY100</t>
+        </is>
+      </c>
+      <c r="B6" s="32" t="inlineStr">
+        <is>
+          <t>Cables &amp; data</t>
+        </is>
+      </c>
+      <c r="C6" s="32" t="inlineStr">
+        <is>
+          <t>DMX &amp; data cables</t>
+        </is>
+      </c>
+      <c r="D6" s="32" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="E6" s="32" t="inlineStr">
+        <is>
+          <t>Neutrik</t>
+        </is>
+      </c>
+      <c r="F6" s="32" t="inlineStr">
+        <is>
+          <t>8-way data 100 m</t>
+        </is>
+      </c>
+      <c r="G6" s="32" t="inlineStr">
+        <is>
+          <t>Neutrik 8-way data multicable 100 m</t>
+        </is>
+      </c>
       <c r="H6" s="42" t="n"/>
       <c r="I6" s="32" t="n"/>
       <c r="J6" s="43" t="n"/>
@@ -1246,7 +1395,24 @@
         <v/>
       </c>
       <c r="P6" s="43" t="n"/>
-      <c r="Q6" s="32" t="n"/>
+      <c r="Q6" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" s="29" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="U6" s="29" t="inlineStr">
+        <is>
+          <t>XLR 5p (DMX)</t>
+        </is>
+      </c>
+      <c r="Y6" s="29" t="inlineStr">
+        <is>
+          <t>dmx, multi</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="30">
       <c r="A7" s="32" t="n"/>
@@ -32336,4 +32502,1230 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D70"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" style="30" min="1" max="1"/>
+    <col width="34" customWidth="1" style="30" min="2" max="2"/>
+    <col width="12" customWidth="1" style="30" min="3" max="3"/>
+    <col width="60" customWidth="1" style="30" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="57" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" s="57" t="inlineStr">
+        <is>
+          <t>Subcategory</t>
+        </is>
+      </c>
+      <c r="C1" s="57" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="D1" s="57" t="inlineStr">
+        <is>
+          <t>Attributes for this subcategory</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>Audio</t>
+        </is>
+      </c>
+      <c r="B2" s="29" t="inlineStr">
+        <is>
+          <t>Speakers</t>
+        </is>
+      </c>
+      <c r="C2" s="29" t="inlineStr">
+        <is>
+          <t>AUDSPK</t>
+        </is>
+      </c>
+      <c r="D2" s="29" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="29" t="inlineStr">
+        <is>
+          <t>Audio</t>
+        </is>
+      </c>
+      <c r="B3" s="29" t="inlineStr">
+        <is>
+          <t>Subwoofers</t>
+        </is>
+      </c>
+      <c r="C3" s="29" t="inlineStr">
+        <is>
+          <t>AUDSUB</t>
+        </is>
+      </c>
+      <c r="D3" s="29" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>Audio</t>
+        </is>
+      </c>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>Speaker rigging &amp; stands</t>
+        </is>
+      </c>
+      <c r="C4" s="29" t="inlineStr">
+        <is>
+          <t>AUDSRG</t>
+        </is>
+      </c>
+      <c r="D4" s="29" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>Audio</t>
+        </is>
+      </c>
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>Amplifiers &amp; processing</t>
+        </is>
+      </c>
+      <c r="C5" s="29" t="inlineStr">
+        <is>
+          <t>AUDAMP</t>
+        </is>
+      </c>
+      <c r="D5" s="29" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>Audio</t>
+        </is>
+      </c>
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>Mixing consoles</t>
+        </is>
+      </c>
+      <c r="C6" s="29" t="inlineStr">
+        <is>
+          <t>AUDCON</t>
+        </is>
+      </c>
+      <c r="D6" s="29" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>Audio</t>
+        </is>
+      </c>
+      <c r="B7" s="29" t="inlineStr">
+        <is>
+          <t>Microphones</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="inlineStr">
+        <is>
+          <t>AUDMIC</t>
+        </is>
+      </c>
+      <c r="D7" s="29" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>Audio</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>Wireless microphones</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="inlineStr">
+        <is>
+          <t>AUDWMI</t>
+        </is>
+      </c>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>Frequency band, Frequency range</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>Audio</t>
+        </is>
+      </c>
+      <c r="B9" s="29" t="inlineStr">
+        <is>
+          <t>In-ear monitoring</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="inlineStr">
+        <is>
+          <t>AUDIEM</t>
+        </is>
+      </c>
+      <c r="D9" s="29" t="inlineStr">
+        <is>
+          <t>Frequency band, Frequency range</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>Audio</t>
+        </is>
+      </c>
+      <c r="B10" s="29" t="inlineStr">
+        <is>
+          <t>Microphone stands</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="inlineStr">
+        <is>
+          <t>AUDMST</t>
+        </is>
+      </c>
+      <c r="D10" s="29" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>Audio</t>
+        </is>
+      </c>
+      <c r="B11" s="29" t="inlineStr">
+        <is>
+          <t>DI boxes &amp; splitters</t>
+        </is>
+      </c>
+      <c r="C11" s="29" t="inlineStr">
+        <is>
+          <t>AUDDIB</t>
+        </is>
+      </c>
+      <c r="D11" s="29" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>Audio</t>
+        </is>
+      </c>
+      <c r="B12" s="29" t="inlineStr">
+        <is>
+          <t>Intercom</t>
+        </is>
+      </c>
+      <c r="C12" s="29" t="inlineStr">
+        <is>
+          <t>AUDINT</t>
+        </is>
+      </c>
+      <c r="D12" s="29" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>Audio</t>
+        </is>
+      </c>
+      <c r="B13" s="29" t="inlineStr">
+        <is>
+          <t>Players, recorders &amp; DJ</t>
+        </is>
+      </c>
+      <c r="C13" s="29" t="inlineStr">
+        <is>
+          <t>AUDPLY</t>
+        </is>
+      </c>
+      <c r="D13" s="29" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>Audio</t>
+        </is>
+      </c>
+      <c r="B14" s="29" t="inlineStr">
+        <is>
+          <t>Effects &amp; outboard</t>
+        </is>
+      </c>
+      <c r="C14" s="29" t="inlineStr">
+        <is>
+          <t>AUDOUT</t>
+        </is>
+      </c>
+      <c r="D14" s="29" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t>Audio</t>
+        </is>
+      </c>
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t>Audio accessories</t>
+        </is>
+      </c>
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t>AUDACC</t>
+        </is>
+      </c>
+      <c r="D15" s="29" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>Lighting</t>
+        </is>
+      </c>
+      <c r="B16" s="29" t="inlineStr">
+        <is>
+          <t>Moving heads</t>
+        </is>
+      </c>
+      <c r="C16" s="29" t="inlineStr">
+        <is>
+          <t>LIGMOV</t>
+        </is>
+      </c>
+      <c r="D16" s="29" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="29" t="inlineStr">
+        <is>
+          <t>Lighting</t>
+        </is>
+      </c>
+      <c r="B17" s="29" t="inlineStr">
+        <is>
+          <t>Profiles &amp; spots</t>
+        </is>
+      </c>
+      <c r="C17" s="29" t="inlineStr">
+        <is>
+          <t>LIGPRO</t>
+        </is>
+      </c>
+      <c r="D17" s="29" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>Lighting</t>
+        </is>
+      </c>
+      <c r="B18" s="29" t="inlineStr">
+        <is>
+          <t>Wash, PAR &amp; panels</t>
+        </is>
+      </c>
+      <c r="C18" s="29" t="inlineStr">
+        <is>
+          <t>LIGWAS</t>
+        </is>
+      </c>
+      <c r="D18" s="29" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="29" t="inlineStr">
+        <is>
+          <t>Lighting</t>
+        </is>
+      </c>
+      <c r="B19" s="29" t="inlineStr">
+        <is>
+          <t>Battens, strobes &amp; blinders</t>
+        </is>
+      </c>
+      <c r="C19" s="29" t="inlineStr">
+        <is>
+          <t>LIGBAT</t>
+        </is>
+      </c>
+      <c r="D19" s="29" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="29" t="inlineStr">
+        <is>
+          <t>Lighting</t>
+        </is>
+      </c>
+      <c r="B20" s="29" t="inlineStr">
+        <is>
+          <t>Film &amp; TV lighting</t>
+        </is>
+      </c>
+      <c r="C20" s="29" t="inlineStr">
+        <is>
+          <t>LIGFTV</t>
+        </is>
+      </c>
+      <c r="D20" s="29" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="29" t="inlineStr">
+        <is>
+          <t>Lighting</t>
+        </is>
+      </c>
+      <c r="B21" s="29" t="inlineStr">
+        <is>
+          <t>Follow spots</t>
+        </is>
+      </c>
+      <c r="C21" s="29" t="inlineStr">
+        <is>
+          <t>LIGFOL</t>
+        </is>
+      </c>
+      <c r="D21" s="29" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="29" t="inlineStr">
+        <is>
+          <t>Lighting</t>
+        </is>
+      </c>
+      <c r="B22" s="29" t="inlineStr">
+        <is>
+          <t>Expo &amp; decorative</t>
+        </is>
+      </c>
+      <c r="C22" s="29" t="inlineStr">
+        <is>
+          <t>LIGEXP</t>
+        </is>
+      </c>
+      <c r="D22" s="29" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>Lighting</t>
+        </is>
+      </c>
+      <c r="B23" s="29" t="inlineStr">
+        <is>
+          <t>Effects &amp; atmosphere</t>
+        </is>
+      </c>
+      <c r="C23" s="29" t="inlineStr">
+        <is>
+          <t>LIGATM</t>
+        </is>
+      </c>
+      <c r="D23" s="29" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="29" t="inlineStr">
+        <is>
+          <t>Lighting</t>
+        </is>
+      </c>
+      <c r="B24" s="29" t="inlineStr">
+        <is>
+          <t>Lighting control &amp; network</t>
+        </is>
+      </c>
+      <c r="C24" s="29" t="inlineStr">
+        <is>
+          <t>LIGCTL</t>
+        </is>
+      </c>
+      <c r="D24" s="29" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="29" t="inlineStr">
+        <is>
+          <t>Lighting</t>
+        </is>
+      </c>
+      <c r="B25" s="29" t="inlineStr">
+        <is>
+          <t>Lighting accessories</t>
+        </is>
+      </c>
+      <c r="C25" s="29" t="inlineStr">
+        <is>
+          <t>LIGACC</t>
+        </is>
+      </c>
+      <c r="D25" s="29" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="29" t="inlineStr">
+        <is>
+          <t>Video</t>
+        </is>
+      </c>
+      <c r="B26" s="29" t="inlineStr">
+        <is>
+          <t>LED screens</t>
+        </is>
+      </c>
+      <c r="C26" s="29" t="inlineStr">
+        <is>
+          <t>VIDLED</t>
+        </is>
+      </c>
+      <c r="D26" s="29" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="29" t="inlineStr">
+        <is>
+          <t>Video</t>
+        </is>
+      </c>
+      <c r="B27" s="29" t="inlineStr">
+        <is>
+          <t>LED processing</t>
+        </is>
+      </c>
+      <c r="C27" s="29" t="inlineStr">
+        <is>
+          <t>VIDLEP</t>
+        </is>
+      </c>
+      <c r="D27" s="29" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="29" t="inlineStr">
+        <is>
+          <t>Video</t>
+        </is>
+      </c>
+      <c r="B28" s="29" t="inlineStr">
+        <is>
+          <t>Projectors</t>
+        </is>
+      </c>
+      <c r="C28" s="29" t="inlineStr">
+        <is>
+          <t>VIDPRJ</t>
+        </is>
+      </c>
+      <c r="D28" s="29" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="29" t="inlineStr">
+        <is>
+          <t>Video</t>
+        </is>
+      </c>
+      <c r="B29" s="29" t="inlineStr">
+        <is>
+          <t>Projector lenses &amp; accessories</t>
+        </is>
+      </c>
+      <c r="C29" s="29" t="inlineStr">
+        <is>
+          <t>VIDLNS</t>
+        </is>
+      </c>
+      <c r="D29" s="29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="29" t="inlineStr">
+        <is>
+          <t>Video</t>
+        </is>
+      </c>
+      <c r="B30" s="29" t="inlineStr">
+        <is>
+          <t>Projection screens</t>
+        </is>
+      </c>
+      <c r="C30" s="29" t="inlineStr">
+        <is>
+          <t>VIDSCR</t>
+        </is>
+      </c>
+      <c r="D30" s="29" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="29" t="inlineStr">
+        <is>
+          <t>Video</t>
+        </is>
+      </c>
+      <c r="B31" s="29" t="inlineStr">
+        <is>
+          <t>Displays &amp; monitors</t>
+        </is>
+      </c>
+      <c r="C31" s="29" t="inlineStr">
+        <is>
+          <t>VIDDSP</t>
+        </is>
+      </c>
+      <c r="D31" s="29" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="29" t="inlineStr">
+        <is>
+          <t>Video</t>
+        </is>
+      </c>
+      <c r="B32" s="29" t="inlineStr">
+        <is>
+          <t>Cameras &amp; lenses</t>
+        </is>
+      </c>
+      <c r="C32" s="29" t="inlineStr">
+        <is>
+          <t>VIDCAM</t>
+        </is>
+      </c>
+      <c r="D32" s="29" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="29" t="inlineStr">
+        <is>
+          <t>Video</t>
+        </is>
+      </c>
+      <c r="B33" s="29" t="inlineStr">
+        <is>
+          <t>Switchers &amp; mixers</t>
+        </is>
+      </c>
+      <c r="C33" s="29" t="inlineStr">
+        <is>
+          <t>VIDSWI</t>
+        </is>
+      </c>
+      <c r="D33" s="29" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="29" t="inlineStr">
+        <is>
+          <t>Video</t>
+        </is>
+      </c>
+      <c r="B34" s="29" t="inlineStr">
+        <is>
+          <t>Signal processing &amp; fibre</t>
+        </is>
+      </c>
+      <c r="C34" s="29" t="inlineStr">
+        <is>
+          <t>VIDSIG</t>
+        </is>
+      </c>
+      <c r="D34" s="29" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="29" t="inlineStr">
+        <is>
+          <t>Video</t>
+        </is>
+      </c>
+      <c r="B35" s="29" t="inlineStr">
+        <is>
+          <t>Media servers &amp; playout</t>
+        </is>
+      </c>
+      <c r="C35" s="29" t="inlineStr">
+        <is>
+          <t>VIDMED</t>
+        </is>
+      </c>
+      <c r="D35" s="29" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="29" t="inlineStr">
+        <is>
+          <t>Video</t>
+        </is>
+      </c>
+      <c r="B36" s="29" t="inlineStr">
+        <is>
+          <t>IT &amp; computers</t>
+        </is>
+      </c>
+      <c r="C36" s="29" t="inlineStr">
+        <is>
+          <t>VIDITC</t>
+        </is>
+      </c>
+      <c r="D36" s="29" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="29" t="inlineStr">
+        <is>
+          <t>Rigging &amp; truss</t>
+        </is>
+      </c>
+      <c r="B37" s="29" t="inlineStr">
+        <is>
+          <t>Square truss</t>
+        </is>
+      </c>
+      <c r="C37" s="29" t="inlineStr">
+        <is>
+          <t>RIGSQU</t>
+        </is>
+      </c>
+      <c r="D37" s="29" t="inlineStr">
+        <is>
+          <t>Length, Colour, Truss series</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="29" t="inlineStr">
+        <is>
+          <t>Rigging &amp; truss</t>
+        </is>
+      </c>
+      <c r="B38" s="29" t="inlineStr">
+        <is>
+          <t>Triangle truss</t>
+        </is>
+      </c>
+      <c r="C38" s="29" t="inlineStr">
+        <is>
+          <t>RIGTRI</t>
+        </is>
+      </c>
+      <c r="D38" s="29" t="inlineStr">
+        <is>
+          <t>Length, Colour, Truss series</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="29" t="inlineStr">
+        <is>
+          <t>Rigging &amp; truss</t>
+        </is>
+      </c>
+      <c r="B39" s="29" t="inlineStr">
+        <is>
+          <t>Ladder &amp; tube truss</t>
+        </is>
+      </c>
+      <c r="C39" s="29" t="inlineStr">
+        <is>
+          <t>RIGLAD</t>
+        </is>
+      </c>
+      <c r="D39" s="29" t="inlineStr">
+        <is>
+          <t>Length, Colour, Truss series</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="29" t="inlineStr">
+        <is>
+          <t>Rigging &amp; truss</t>
+        </is>
+      </c>
+      <c r="B40" s="29" t="inlineStr">
+        <is>
+          <t>Rectangle &amp; pre-rig truss</t>
+        </is>
+      </c>
+      <c r="C40" s="29" t="inlineStr">
+        <is>
+          <t>RIGREC</t>
+        </is>
+      </c>
+      <c r="D40" s="29" t="inlineStr">
+        <is>
+          <t>Length, Colour, Truss series</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="29" t="inlineStr">
+        <is>
+          <t>Rigging &amp; truss</t>
+        </is>
+      </c>
+      <c r="B41" s="29" t="inlineStr">
+        <is>
+          <t>Circle truss</t>
+        </is>
+      </c>
+      <c r="C41" s="29" t="inlineStr">
+        <is>
+          <t>RIGCIR</t>
+        </is>
+      </c>
+      <c r="D41" s="29" t="inlineStr">
+        <is>
+          <t>Colour, Truss series</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="29" t="inlineStr">
+        <is>
+          <t>Rigging &amp; truss</t>
+        </is>
+      </c>
+      <c r="B42" s="29" t="inlineStr">
+        <is>
+          <t>Ground support &amp; towers</t>
+        </is>
+      </c>
+      <c r="C42" s="29" t="inlineStr">
+        <is>
+          <t>RIGGRS</t>
+        </is>
+      </c>
+      <c r="D42" s="29" t="inlineStr">
+        <is>
+          <t>Colour, Truss series</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="29" t="inlineStr">
+        <is>
+          <t>Rigging &amp; truss</t>
+        </is>
+      </c>
+      <c r="B43" s="29" t="inlineStr">
+        <is>
+          <t>Truss accessories</t>
+        </is>
+      </c>
+      <c r="C43" s="29" t="inlineStr">
+        <is>
+          <t>RIGTAC</t>
+        </is>
+      </c>
+      <c r="D43" s="29" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="29" t="inlineStr">
+        <is>
+          <t>Rigging &amp; truss</t>
+        </is>
+      </c>
+      <c r="B44" s="29" t="inlineStr">
+        <is>
+          <t>Hoists &amp; controllers</t>
+        </is>
+      </c>
+      <c r="C44" s="29" t="inlineStr">
+        <is>
+          <t>RIGHOI</t>
+        </is>
+      </c>
+      <c r="D44" s="29" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="29" t="inlineStr">
+        <is>
+          <t>Rigging &amp; truss</t>
+        </is>
+      </c>
+      <c r="B45" s="29" t="inlineStr">
+        <is>
+          <t>Rigging hardware &amp; load cells</t>
+        </is>
+      </c>
+      <c r="C45" s="29" t="inlineStr">
+        <is>
+          <t>RIGHAR</t>
+        </is>
+      </c>
+      <c r="D45" s="29" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="29" t="inlineStr">
+        <is>
+          <t>Rigging &amp; truss</t>
+        </is>
+      </c>
+      <c r="B46" s="29" t="inlineStr">
+        <is>
+          <t>Lifts &amp; stands</t>
+        </is>
+      </c>
+      <c r="C46" s="29" t="inlineStr">
+        <is>
+          <t>RIGLIF</t>
+        </is>
+      </c>
+      <c r="D46" s="29" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="29" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="B47" s="29" t="inlineStr">
+        <is>
+          <t>Power distribution</t>
+        </is>
+      </c>
+      <c r="C47" s="29" t="inlineStr">
+        <is>
+          <t>POWDIS</t>
+        </is>
+      </c>
+      <c r="D47" s="29" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="29" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="B48" s="29" t="inlineStr">
+        <is>
+          <t>Power cables &amp; kits</t>
+        </is>
+      </c>
+      <c r="C48" s="29" t="inlineStr">
+        <is>
+          <t>POWCAB</t>
+        </is>
+      </c>
+      <c r="D48" s="29" t="inlineStr">
+        <is>
+          <t>Length, Connector</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="29" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="B49" s="29" t="inlineStr">
+        <is>
+          <t>Transformers &amp; UPS</t>
+        </is>
+      </c>
+      <c r="C49" s="29" t="inlineStr">
+        <is>
+          <t>POWTRF</t>
+        </is>
+      </c>
+      <c r="D49" s="29" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="29" t="inlineStr">
+        <is>
+          <t>Staging</t>
+        </is>
+      </c>
+      <c r="B50" s="29" t="inlineStr">
+        <is>
+          <t>Stage platforms</t>
+        </is>
+      </c>
+      <c r="C50" s="29" t="inlineStr">
+        <is>
+          <t>STAPLA</t>
+        </is>
+      </c>
+      <c r="D50" s="29" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="29" t="inlineStr">
+        <is>
+          <t>Staging</t>
+        </is>
+      </c>
+      <c r="B51" s="29" t="inlineStr">
+        <is>
+          <t>Circular stages</t>
+        </is>
+      </c>
+      <c r="C51" s="29" t="inlineStr">
+        <is>
+          <t>STACIR</t>
+        </is>
+      </c>
+      <c r="D51" s="29" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="29" t="inlineStr">
+        <is>
+          <t>Staging</t>
+        </is>
+      </c>
+      <c r="B52" s="29" t="inlineStr">
+        <is>
+          <t>Stage legs &amp; accessories</t>
+        </is>
+      </c>
+      <c r="C52" s="29" t="inlineStr">
+        <is>
+          <t>STASAC</t>
+        </is>
+      </c>
+      <c r="D52" s="29" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="29" t="inlineStr">
+        <is>
+          <t>Staging</t>
+        </is>
+      </c>
+      <c r="B53" s="29" t="inlineStr">
+        <is>
+          <t>Pipe &amp; drape</t>
+        </is>
+      </c>
+      <c r="C53" s="29" t="inlineStr">
+        <is>
+          <t>STADRA</t>
+        </is>
+      </c>
+      <c r="D53" s="29" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="29" t="inlineStr">
+        <is>
+          <t>Cables &amp; data</t>
+        </is>
+      </c>
+      <c r="B54" s="29" t="inlineStr">
+        <is>
+          <t>Audio multicores &amp; breakouts</t>
+        </is>
+      </c>
+      <c r="C54" s="29" t="inlineStr">
+        <is>
+          <t>CABAMC</t>
+        </is>
+      </c>
+      <c r="D54" s="29" t="inlineStr">
+        <is>
+          <t>Length, Connector</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="29" t="inlineStr">
+        <is>
+          <t>Cables &amp; data</t>
+        </is>
+      </c>
+      <c r="B55" s="29" t="inlineStr">
+        <is>
+          <t>DMX &amp; data cables</t>
+        </is>
+      </c>
+      <c r="C55" s="29" t="inlineStr">
+        <is>
+          <t>CABDAT</t>
+        </is>
+      </c>
+      <c r="D55" s="29" t="inlineStr">
+        <is>
+          <t>Length, Connector</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="29" t="inlineStr">
+        <is>
+          <t>Cables &amp; data</t>
+        </is>
+      </c>
+      <c r="B56" s="29" t="inlineStr">
+        <is>
+          <t>Fibre &amp; video cables</t>
+        </is>
+      </c>
+      <c r="C56" s="29" t="inlineStr">
+        <is>
+          <t>CABFIB</t>
+        </is>
+      </c>
+      <c r="D56" s="29" t="inlineStr">
+        <is>
+          <t>Length, Connector</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="29" t="inlineStr">
+        <is>
+          <t>Cables &amp; data</t>
+        </is>
+      </c>
+      <c r="B57" s="29" t="inlineStr">
+        <is>
+          <t>Adapters &amp; special cables</t>
+        </is>
+      </c>
+      <c r="C57" s="29" t="inlineStr">
+        <is>
+          <t>CABADP</t>
+        </is>
+      </c>
+      <c r="D57" s="29" t="inlineStr">
+        <is>
+          <t>Length, Connector</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="29" t="inlineStr">
+        <is>
+          <t>Cables &amp; data</t>
+        </is>
+      </c>
+      <c r="B58" s="29" t="inlineStr">
+        <is>
+          <t>Cable protection</t>
+        </is>
+      </c>
+      <c r="C58" s="29" t="inlineStr">
+        <is>
+          <t>CABPRT</t>
+        </is>
+      </c>
+      <c r="D58" s="29" t="inlineStr"/>
+    </row>
+    <row r="59"/>
+    <row r="60">
+      <c r="A60" s="58" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="B60" s="58" t="inlineStr">
+        <is>
+          <t>Choices (one per cell, or several separated by a comma where allowed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="29" t="inlineStr">
+        <is>
+          <t>Length (m)</t>
+        </is>
+      </c>
+      <c r="B61" s="29" t="inlineStr">
+        <is>
+          <t>0.21, 0.25, 0.29, 0.38, 0.4, 0.5, 0.6, 0.69, 0.71, 0.75, 0.79, 0.8, 0.81, 1, 1.2, 1.22, 1.5, 1.6, 2, 2.4, 2.44, 2.5, 3, 4, 5, 10, 15, 20, 25, 30, 35, 50, 75, 90, 100, 150, 300</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="29" t="inlineStr">
+        <is>
+          <t>Frequency band · several</t>
+        </is>
+      </c>
+      <c r="B62" s="29" t="inlineStr">
+        <is>
+          <t>G51, H51, K52, G10E, K10E, AW, BW, CW, GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="29" t="inlineStr">
+        <is>
+          <t>Frequency range (MHz)</t>
+        </is>
+      </c>
+      <c r="B63" s="29" t="inlineStr">
+        <is>
+          <t>450–950, 450–960, 460–900, 470–558 / 550–638, 470–636, 470–638, 470–698, 470–790, 470–798, 470–865, 470–866, 470–870, 470–960, 470–1100, 500–870, 500–900</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="29" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="B64" s="29" t="inlineStr">
+        <is>
+          <t>XLR 3p, XLR 5p (DMX), LK150, Harting 16p, Harting 24p, Socapex 19p, Veam, Proplex 3p, Schaltbau, opticalCON DUO, opticalCON MTP24, Lemo fibre, Fibreco, CEE 16 A, CEE 32 A, CEE 63 A, CEE 125 A, Schuko, powerCON, etherCON</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="29" t="inlineStr">
+        <is>
+          <t>Colour</t>
+        </is>
+      </c>
+      <c r="B65" s="29" t="inlineStr">
+        <is>
+          <t>Aluminium, Black</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="29" t="inlineStr">
+        <is>
+          <t>Truss series</t>
+        </is>
+      </c>
+      <c r="B66" s="29" t="inlineStr">
+        <is>
+          <t>NH11, NH32, NX33, NH33, NH34, NH44, NS52, NSL52, NSL66, NSR36, NBR100, NSPR36, P36ADT, NBT52, NST44, NT30, NT40, NT50</t>
+        </is>
+      </c>
+    </row>
+    <row r="67"/>
+    <row r="68">
+      <c r="A68" s="58" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="B68" s="29" t="inlineStr">
+        <is>
+          <t>Featured, New, Complete set, Outdoor (IP65), Battery powered, Wireless, Low noise</t>
+        </is>
+      </c>
+    </row>
+    <row r="69"/>
+    <row r="70">
+      <c r="A70" s="29" t="inlineStr">
+        <is>
+          <t>Names in Dutch, French or Spanish and the codes are accepted too. Unknown values stop that row with a clear message. The lists are managed in Settings › Product categories.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/resources/templates/CLUK_Import_Templates.xlsx
+++ b/resources/templates/CLUK_Import_Templates.xlsx
@@ -174,7 +174,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -346,6 +346,7 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -891,7 +892,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="29" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:X501"/>
+  <dimension ref="A1:AA501"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="13" customWidth="1" style="29" min="1" max="2"/>
@@ -12354,6 +12354,9 @@
     <col width="14" customWidth="1" style="29" min="21" max="21"/>
     <col width="11" customWidth="1" style="29" min="22" max="22"/>
     <col width="13" customWidth="1" style="29" min="23" max="24"/>
+    <col width="18" customWidth="1" style="30" min="25" max="25"/>
+    <col width="18" customWidth="1" style="30" min="26" max="26"/>
+    <col width="18" customWidth="1" style="30" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1" s="30">
@@ -12475,6 +12478,21 @@
       <c r="X1" s="47" t="inlineStr">
         <is>
           <t>Margin at list price (calculated)</t>
+        </is>
+      </c>
+      <c r="Y1" s="35" t="inlineStr">
+        <is>
+          <t>Sub-Category</t>
+        </is>
+      </c>
+      <c r="Z1" s="35" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="AA1" s="35" t="inlineStr">
+        <is>
+          <t>Search words</t>
         </is>
       </c>
     </row>
@@ -32510,7 +32528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D70"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="30" min="1" max="1"/>
@@ -33619,7 +33637,6 @@
       </c>
       <c r="D58" s="29" t="inlineStr"/>
     </row>
-    <row r="59"/>
     <row r="60">
       <c r="A60" s="58" t="inlineStr">
         <is>
@@ -33704,7 +33721,6 @@
         </is>
       </c>
     </row>
-    <row r="67"/>
     <row r="68">
       <c r="A68" s="58" t="inlineStr">
         <is>
@@ -33717,11 +33733,118 @@
         </is>
       </c>
     </row>
-    <row r="69"/>
     <row r="70">
       <c r="A70" s="29" t="inlineStr">
         <is>
           <t>Names in Dutch, French or Spanish and the codes are accepted too. Unknown values stop that row with a clear message. The lists are managed in Settings › Product categories.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="59" t="inlineStr">
+        <is>
+          <t>Sales products: categories</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Sub-Category</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Audio</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Lighting</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Video</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Connectors</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Rigging</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Consumables</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Cases</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>General</t>
         </is>
       </c>
     </row>

--- a/resources/templates/CLUK_Import_Templates.xlsx
+++ b/resources/templates/CLUK_Import_Templates.xlsx
@@ -12329,7 +12329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AA501"/>
+  <dimension ref="A1:AB501"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="13" customWidth="1" style="29" min="1" max="2"/>
@@ -12357,6 +12357,7 @@
     <col width="18" customWidth="1" style="30" min="25" max="25"/>
     <col width="18" customWidth="1" style="30" min="26" max="26"/>
     <col width="18" customWidth="1" style="30" min="27" max="27"/>
+    <col width="22" customWidth="1" style="30" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1" s="30">
@@ -12493,6 +12494,11 @@
       <c r="AA1" s="35" t="inlineStr">
         <is>
           <t>Search words</t>
+        </is>
+      </c>
+      <c r="AB1" s="35" t="inlineStr">
+        <is>
+          <t>Manufacturer code</t>
         </is>
       </c>
     </row>
@@ -12577,6 +12583,11 @@
         <f>IF(OR(W2="",G2=0),"",ROUND(1-W2/G2,3))</f>
         <v/>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>SM58-LCE</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="30">
       <c r="A3" s="48" t="n"/>
@@ -12659,6 +12670,11 @@
         <f>IF(OR(W3="",G3=0),"",ROUND(1-W3/G3,3))</f>
         <v/>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>EW-D 835-S (R1-6)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="30">
       <c r="A4" s="48" t="n"/>
@@ -12740,6 +12756,11 @@
       <c r="X4" s="52">
         <f>IF(OR(W4="",G4=0),"",ROUND(1-W4/G4,3))</f>
         <v/>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>GAF50BK</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="30">
@@ -33746,103 +33767,103 @@
           <t>Sales products: categories</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="29" t="inlineStr">
         <is>
           <t>Sub-Category</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="29" t="inlineStr">
         <is>
           <t>Audio</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="29" t="inlineStr">
         <is>
           <t>Lighting</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="29" t="inlineStr">
         <is>
           <t>Video</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="29" t="inlineStr">
         <is>
           <t>Connectors</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="29" t="inlineStr">
         <is>
           <t>Rigging</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="29" t="inlineStr">
         <is>
           <t>Consumables</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="29" t="inlineStr">
         <is>
           <t>Cases</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="29" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
